--- a/final_data_pipeline/output/325194longform_elec_options.xlsx
+++ b/final_data_pipeline/output/325194longform_elec_options.xlsx
@@ -597,7 +597,7 @@
         <v>43</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="L2">
         <v>8000</v>
@@ -612,10 +612,10 @@
         <v>1526326.472640449</v>
       </c>
       <c r="R2">
-        <v>1.052935222672065</v>
+        <v>1.105721877767936</v>
       </c>
       <c r="S2">
-        <v>1.086814345991561</v>
+        <v>1.143718778908418</v>
       </c>
       <c r="T2">
         <v>190.7908090800561</v>
@@ -650,7 +650,7 @@
         <v>44</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="L3">
         <v>8000</v>
@@ -997,7 +997,7 @@
         <v>43</v>
       </c>
       <c r="K10">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L10">
         <v>8000</v>
@@ -1012,10 +1012,10 @@
         <v>358787.9976041867</v>
       </c>
       <c r="R10">
-        <v>1.052935222672065</v>
+        <v>1.004851086664878</v>
       </c>
       <c r="S10">
-        <v>1.086814345991561</v>
+        <v>1.035188389617639</v>
       </c>
       <c r="T10">
         <v>44.84849970052334</v>
@@ -1050,7 +1050,7 @@
         <v>44</v>
       </c>
       <c r="K11">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L11">
         <v>8000</v>
@@ -1397,7 +1397,7 @@
         <v>44</v>
       </c>
       <c r="K18">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="L18">
         <v>8000</v>
@@ -1444,7 +1444,7 @@
         <v>43</v>
       </c>
       <c r="K19">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="L19">
         <v>8000</v>
@@ -1459,10 +1459,10 @@
         <v>260213.1745406333</v>
       </c>
       <c r="R19">
-        <v>1.052935222672065</v>
+        <v>1.103333005990376</v>
       </c>
       <c r="S19">
-        <v>1.086814345991561</v>
+        <v>1.14113834478515</v>
       </c>
       <c r="T19">
         <v>32.52664681757916</v>
@@ -1597,7 +1597,7 @@
         <v>44</v>
       </c>
       <c r="K22">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="L22">
         <v>8000</v>
@@ -1644,7 +1644,7 @@
         <v>43</v>
       </c>
       <c r="K23">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="L23">
         <v>8000</v>
@@ -1659,10 +1659,10 @@
         <v>1032763.989452207</v>
       </c>
       <c r="R23">
-        <v>1.052935222672065</v>
+        <v>1.065614691876665</v>
       </c>
       <c r="S23">
-        <v>1.086814345991561</v>
+        <v>1.100460934966844</v>
       </c>
       <c r="T23">
         <v>129.0954986815259</v>
